--- a/public/template/products-import-template.xlsx
+++ b/public/template/products-import-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -34,25 +34,103 @@
     <t>Low stock threshold</t>
   </si>
   <si>
-    <t>Sample notebook</t>
-  </si>
-  <si>
-    <t>NB-001</t>
-  </si>
-  <si>
-    <t>Spiral bound A5</t>
-  </si>
-  <si>
-    <t>Office chair</t>
-  </si>
-  <si>
-    <t>CHAIR-02</t>
-  </si>
-  <si>
-    <t>Ergonomic mesh</t>
+    <t>Hardcover Notebook A5</t>
+  </si>
+  <si>
+    <t>ACME-NB-A5</t>
+  </si>
+  <si>
+    <t>Ruled, 192 pages</t>
+  </si>
+  <si>
+    <t>Ballpoint Pen Blue (box 50)</t>
+  </si>
+  <si>
+    <t>ACME-PEN-BLU-50</t>
+  </si>
+  <si>
+    <t>Smooth gel ink</t>
+  </si>
+  <si>
+    <t>Sticky Notes 3x3 Neon</t>
+  </si>
+  <si>
+    <t>ACME-STICKY-3N</t>
+  </si>
+  <si>
+    <t>12 pads per carton</t>
+  </si>
+  <si>
+    <t>Ring Binder 2"</t>
+  </si>
+  <si>
+    <t>ACME-BIND-2IN</t>
+  </si>
+  <si>
+    <t>D-ring, black</t>
+  </si>
+  <si>
+    <t>Highlighter Set 6-color</t>
+  </si>
+  <si>
+    <t>ACME-HI-SET6</t>
+  </si>
+  <si>
+    <t>Chisel tip</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Desktop Stapler Heavy Duty</t>
+  </si>
+  <si>
+    <t>ACME-STAP-HD</t>
+  </si>
+  <si>
+    <t>25-sheet capacity</t>
+  </si>
+  <si>
+    <t>Arabica Whole Bean 1kg</t>
+  </si>
+  <si>
+    <t>GLX-COF-ARB-1K</t>
+  </si>
+  <si>
+    <t>Medium roast</t>
+  </si>
+  <si>
+    <t>Earl Grey Loose Leaf 250g</t>
+  </si>
+  <si>
+    <t>GLX-TEA-EG-250</t>
+  </si>
+  <si>
+    <t>Citrus bergamot</t>
+  </si>
+  <si>
+    <t>Ceramic Mug 12oz Matte Black</t>
+  </si>
+  <si>
+    <t>GLX-MUG-12-BK</t>
+  </si>
+  <si>
+    <t>Dishwasher safe</t>
+  </si>
+  <si>
+    <t>Cane Sugar 1kg</t>
+  </si>
+  <si>
+    <t>GLX-SUG-CANE-1K</t>
+  </si>
+  <si>
+    <t>Oat Barista Blend 1L</t>
+  </si>
+  <si>
+    <t>GLX-OAT-BAR-1L</t>
+  </si>
+  <si>
+    <t>Foamable</t>
   </si>
 </sst>
 </file>
@@ -433,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -479,16 +557,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="E2">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F2">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -502,16 +580,223 @@
         <v>12</v>
       </c>
       <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>89</v>
-      </c>
       <c r="F3">
-        <v>149.99</v>
-      </c>
-      <c r="G3" t="s">
+        <v>24.5</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>6.25</v>
+      </c>
+      <c r="F4">
+        <v>12.99</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>42</v>
+      </c>
+      <c r="E5">
+        <v>3.1</v>
+      </c>
+      <c r="F5">
+        <v>7.49</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>55</v>
+      </c>
+      <c r="E6">
+        <v>2.8</v>
+      </c>
+      <c r="F6">
+        <v>6.25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>9.4</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>14.5</v>
+      </c>
+      <c r="F8">
+        <v>28.99</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>8.2</v>
+      </c>
+      <c r="F9">
+        <v>16.5</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10">
+        <v>112</v>
+      </c>
+      <c r="E10">
+        <v>3.5</v>
+      </c>
+      <c r="F10">
+        <v>8.99</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>200</v>
+      </c>
+      <c r="E11">
+        <v>1.4</v>
+      </c>
+      <c r="F11">
+        <v>3.29</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>2.05</v>
+      </c>
+      <c r="F12">
+        <v>4.49</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
